--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$J$193</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="000070C0"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:J193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,39 +467,39 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>data</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ativa</t>
+          <t>score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bolsas e Auxílios</t>
+          <t>Postdoctoral Fellowships</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CNPq</t>
+          <t>MSCA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Pós-doc</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +509,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios</t>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/actions/postdoctoral-fellowships</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -504,16 +517,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bolsas no País e no Exterior</t>
+          <t>Painéis de Dados</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,12 +539,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -543,7 +554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/copy_of_modalidades</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/dados-abertos/paineis-de-dados</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -551,16 +562,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Auxílios</t>
+          <t>Procedimentos e Processos Correcionais</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,12 +584,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -590,7 +599,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-1</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/corregedoria/procedimentos-e-processos-correcionais</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -598,16 +607,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cartão Pesquisa</t>
+          <t>Painel de Corregedorias da Corregedoria Geral da União (CRG)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,12 +629,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -637,7 +644,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-cartao-pesquisa</t>
+          <t>https://centralpaineis.cgu.gov.br/visualizar/corregedorias</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -645,16 +652,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pesquisa em Pauta</t>
+          <t>Painel dos Comitês Assessores</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -669,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -684,7 +689,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/pesquisa-do-dia</t>
+          <t>https://app.powerbi.com/view?r=eyJrIjoiOTYyMGFlMWItOWRmNS00ZTZkLWI2ZGItMmM4YWNhZjQ4YWQxIiwidCI6IjkyYzBjZmE5LTdlOTEtNGVhZC1hYzI5LWNkNDRhMjM4OWIwMSJ9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -692,16 +697,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Relatório de Pesquisa</t>
+          <t>Guias e Tutoriais</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,12 +719,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -731,7 +734,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/assuntos/popularizacao-da-ciencia/relatorios-de-pesquisa</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/comites-assessoramento/guias-e-tutoriais</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -739,16 +742,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sisgen Pesquisa</t>
+          <t>Canais de Atendimento</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -763,12 +764,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -778,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://sisgen-pesquisa.cnpq.br</t>
+          <t>https://www.gov.br/cnpq/pt-br/canais_atendimento</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -786,16 +787,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Serviços para Imigrantes</t>
+          <t>Centrais de Conteúdo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -810,12 +809,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -825,7 +824,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.gov.br/pt-br/temas/servicos-para-imigrantes</t>
+          <t>https://www.gov.br/cnpq/pt-br/centrais-de-conteudo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -833,16 +832,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Educação e Pesquisa</t>
+          <t>Diretoria de Análise de Resultados e Soluções Digitais - DASD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -857,12 +854,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -872,7 +869,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.gov.br/pt-br/noticias/educacao-e-pesquisa</t>
+          <t>https://www.gov.br/cnpq/pt-br/composicao/diretoria-executiva-1/copy_of_diretoria-de-gestao-e-tecnologia-da-informacao-dgti</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -880,16 +877,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bolsas no País e no Exterior</t>
+          <t>Painel dos Comitês Assessores</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -904,12 +899,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -919,7 +914,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/copy_of_modalidades</t>
+          <t>https://app.powerbi.com/view?r=eyJrIjoiOTYyMGFlMWItOWRmNS00ZTZkLWI2ZGItMmM4YWNhZjQ4YWQxIiwidCI6IjkyYzBjZmE5LTdlOTEtNGVhZC1hYzI5LWNkNDRhMjM4OWIwMSJ9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -927,16 +922,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Auxílios</t>
+          <t>Demais segmentos (ONGs, organizações sociais, etc)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -951,12 +944,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -966,7 +959,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-1</t>
+          <t>https://www.gov.br/pt-br/servicos/listar_servicos_segmento?segmento=publico_alvo_outros</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -974,16 +967,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cartão Pesquisa</t>
+          <t>Proteção de Dados Pessoais</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -998,12 +989,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1013,7 +1004,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-cartao-pesquisa</t>
+          <t>https://www.gov.br/pt-br/temas/protecao-de-dados-pessoais</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1021,16 +1012,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Painel de Bolsas e Projetos VigentesFornece uma fotografia do fomento atual do CNPq. Além do número total de projetos ou de bolsas vigentes em cada uma das 13 dimensões disponibilizadas.</t>
+          <t>Serviços para Imigrantes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1045,12 +1034,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1060,7 +1049,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/mapa-de-fomento-em-ciencia-tecnologia-e-inovacao</t>
+          <t>https://www.gov.br/pt-br/temas/servicos-para-imigrantes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1068,16 +1057,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bolsas e Auxílios</t>
+          <t>Política e Orçamento Educacionais</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1092,12 +1079,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1107,7 +1094,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios</t>
+          <t>https://www.gov.br/pt-br/temas/politica-e-orcamento-educacional</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1115,16 +1102,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bolsas no País e no Exterior</t>
+          <t>Canais do Executivo Federal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1139,12 +1124,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1154,7 +1139,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/copy_of_modalidades</t>
+          <t>https://www.gov.br/pt-br/canais-do-executivo-federal</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1162,16 +1147,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Auxílios</t>
+          <t>Painel Estatístico de Pessoal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1186,12 +1169,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1201,7 +1184,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-1</t>
+          <t>https://www.gov.br/gestao/pt-br/acesso-a-informacao/servidores/servidores-publicos/painel-estatistico-de-pessoal</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1209,16 +1192,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cartão Pesquisa</t>
+          <t>Painel de Compras do Governo Federal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1233,12 +1214,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1248,7 +1229,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/auxilios-cartao-pesquisa</t>
+          <t>http://paineldecompras.economia.gov.br</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1256,16 +1237,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pesquisa em Pauta</t>
+          <t>ImóveisNovoConsultar dados e baixar documentos de imóveis rurais na plataforma Meu Imóvel Rural</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1280,12 +1259,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1295,7 +1274,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/pesquisa-do-dia</t>
+          <t>https://www.gov.br/pt-br/servicos/consultar-dados-de-imoveis-rurais-na-plataforma-meu-imovel-rural?origem=destaque_inst</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1303,16 +1282,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Relatório de Pesquisa</t>
+          <t>Saiba mais sobre Chamada de Apoio a Eventos de Promoção do Empreendedorismo e da Inovação: 1ª rodada tem inscrições a...</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1327,12 +1304,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1342,7 +1319,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.gov.br/cnpq/pt-br/assuntos/popularizacao-da-ciencia/relatorios-de-pesquisa</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/chamada-de-apoio-a-eventos-de-promocao-do-empreendedorismo-e-da-inovacao-esta-com-inscricoes-abertas-ate-28-05</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1350,16 +1327,14 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sisgen Pesquisa</t>
+          <t>Saiba mais sobre CNPq apoia projetos sobre métodos alternativos à experimentação animal em pesquisas; inscrições até ...</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1374,12 +1349,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1389,7 +1364,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://sisgen-pesquisa.cnpq.br</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/chamada-renama-nams-cnpq-publica-edital</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1397,21 +1372,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Prêmio CAPES/Fundação Grupo Volkswagen de Excelência em Pesquisa em Mobilidade Urbana Sustentável</t>
+          <t>Saiba mais sobre 75 anos do CNPq: autoridades destacam papel ativo do Conselho na consolidação e expansão da ciência ...</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1421,12 +1394,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1436,7 +1409,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-fundacao-grupo-volkswagen-de-excelencia-em-pesquisa-em-mobilidade-urbana-sustentavel</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/75-anos-de-cnpq-solenidade-reune-autoridades-colaboradores-e-pesquisadores-para-comemorar-data</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1444,21 +1417,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Prêmio CAPES - Natura Campus de Excelência em Pesquisa</t>
+          <t>Saiba mais sobre Novo PCI: chamada investirá R$ 120 milhões em pesquisas de unidades vinculadas ao MCTI; inscrições a...</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,12 +1439,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1483,7 +1454,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-natura</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/cnpq-publicou-edital-do-novo-programa-de-capacitacao-institucional</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1491,21 +1462,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Seminário Estruturas em Aço, Ensino e Pesquisa Científica e Tecnológica.</t>
+          <t>Saiba mais sobre Com carreira dedicada à Amazônia, bióloga Maria Teresa Fernandez Piedade vence Prêmio Almirante Álva...</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1515,12 +1484,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1530,7 +1499,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/seminario-estruturas-em-aco-ensino-e-pesquisa-cientifica-e-tecnologica</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/pesquisadora-maria-teresa-fernandez-piedade-e-a-contemplada-com-o-premio-almirante-alvaro-alberto-2013-edicao-2026-1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1538,21 +1507,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bolsas e Estudantes</t>
+          <t>Saiba mais sobre Prêmio Jovem Cientista 2026: inscrições abertas até 31 de julho</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,12 +1529,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1577,7 +1544,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/premio-jovem-cientista-2026-inscricoes-estao-abertas-ate-31-de-julho</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1585,21 +1552,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Edital seleção</t>
+          <t>Saiba mais sobre Parceria Embrapa-CNPq investe R$ 50 milhões em capacitação agrícola para países africanos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1609,12 +1574,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1624,7 +1589,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servidores/edital-selecao</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/parceria-embrapa-cnpq-investe-r-50-milhoes-em-capacitacao-agricola-para-paises-africanos</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1632,21 +1597,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bolsas e Auxílios Internacionais</t>
+          <t>Saiba mais sobre Chamada Pepe Mujica: prazo de submissões prorrogado até 18/05; confira alterações no edital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1656,12 +1619,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1671,7 +1634,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/bolsas-e-auxilios-internacionais</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/chamada-pepe-mujiga-prazo-de-submissoes-prorrogado-ate-18-05-confira-alteracoes-no-edital</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1679,21 +1642,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Programas e Bolsas no País</t>
+          <t>Saiba mais sobre CNPq celebra 75 anos com solenidade e anúncio de novas ações</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1703,12 +1664,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1718,7 +1679,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/programas-e-bolsas-no-pais</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/cnpq-celebra-75-anos-com-solenidade-e-anuncio-de-novas-acoes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1726,21 +1687,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pesquisa Pública</t>
+          <t>Saiba mais sobre 75 anos do CNPq: Conselho está presente em todas as fases da vida do pesquisador</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1750,12 +1709,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1765,7 +1724,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://sei.capes.gov.br/sei/modulos/pesquisa/md_pesq_processo_pesquisar.php?acao_externa=protocolo_pesquisar&amp;acao_origem_externa=protocolo_pesquisar&amp;id_orgao_acesso_externo=1</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/75-anos-do-cnpq-conselho-esta-presente-em-todas-as-fases-da-vida-do-pesquisador</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1773,21 +1732,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Auxílio Financeiro a Projeto Educacional ou de Pesquisa e Pós-Graduação - AUXPE</t>
+          <t>Saiba mais sobre CNPq lança site e videocast de entrevistas para celebrar os 20 anos do Programa Mulheres e Ciência</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1797,12 +1754,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pós-doc</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1812,7 +1769,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/prestacao-de-contas-e-cobranca-administrativa/auxilio-financeiro-a-projeto-educacional-ou-de-pesquisa-e-pos-graduacao-auxpe</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/cnpq-lanca-site-e-videocast-de-entrevistas-para-celebrar-os-20-anos-do-programa-mulheres-e-ciencia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1820,21 +1777,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Manual Cartão Pesquisador</t>
+          <t>SciDev.Net e EurekAlert! promovem workshop sobre divulgação científica para comunicadores institucionais e assessores...</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1844,12 +1799,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1859,7 +1814,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/09042024_manual-cartao-pesquisador-capes-2024-v04.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/oportunidades-externas/curso-on-line-gratuito-focara-divulgacao-cientifica-para-institucionais-e-assessores-de-imprensa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1867,21 +1822,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Termo Uso e Politica de Privacidade App Pesquisador</t>
+          <t>Painel de Fomento em Ciência, Tecnologia e InovaçãoÉ uma plataforma de apresentação de dados do fomento do CNPq à pes...</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1891,12 +1844,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1906,7 +1859,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/termo-uso-e-politica-de-privacidade-app-pesquisador</t>
+          <t>http://bi.cnpq.br/painel/v2/p-fomento-cti.html</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1914,21 +1867,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Serviços para Imigrantes</t>
+          <t>Painel de Chamadas de Bolsas de Produtividade - PQOs números e gráficos exibidos neste painel refletem as propostas s...</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1938,12 +1889,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1953,7 +1904,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.gov.br/pt-br/temas/servicos-para-imigrantes</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/dados-abertos/paineis-de-dados/painel-de-chamadas-de-bolsas-de-produtividade-pq</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1961,21 +1912,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Educação e Pesquisa</t>
+          <t>Painel de Adicional de BancadaDetalha o pagamento mensal aos bolsistas para custeio de atividades de pesquisa científ...</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1985,12 +1934,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2000,7 +1949,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.gov.br/pt-br/noticias/educacao-e-pesquisa</t>
+          <t>http://bi.cnpq.br/painel/v2/p-adicional-de-bancada.html</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2008,21 +1957,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bolsas e Auxílios Internacionais</t>
+          <t>Painel de Bolsas e Projetos VigentesFornece uma fotografia do fomento atual do CNPq. Além do número total de projetos...</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2032,12 +1979,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2047,7 +1994,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/bolsas-e-auxilios/mapa-de-fomento-em-ciencia-tecnologia-e-inovacao</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2055,21 +2002,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Valores de Bolsas</t>
+          <t>Painel de Demanda e AtendimentoOs dados disponibilizados pelo Painel são fundamentais para a análise sobre a dimensão...</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2079,12 +2024,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2094,7 +2039,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/prestacao-de-contas/valores-de-bolsas</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/dados-abertos/paineis-de-dados/painel-de-demanda-e-atendimento</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2102,21 +2047,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Prêmio CAPES/Fundação Grupo Volkswagen de Excelência em Pesquisa em Mobilidade Urbana Sustentável</t>
+          <t>Painel LattesO Painel Lattes reúne dados extraídos dos currículos dos quase um milhão de mestres e doutores, cadastra...</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2126,12 +2069,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2141,7 +2084,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-fundacao-grupo-volkswagen-de-excelencia-em-pesquisa-em-mobilidade-urbana-sustentavel</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/dados-abertos/paineis-de-dados/painel-lattes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2149,21 +2092,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Prêmio CAPES - Natura Campus de Excelência em Pesquisa</t>
+          <t>Saiba mais sobre os Painéis de Dados</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2173,12 +2114,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2188,7 +2129,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-natura</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/dados-abertos/gestao-transparente-dos-dados-da-ciencia-brasileira</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2196,21 +2137,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Seminário Estruturas em Aço, Ensino e Pesquisa Científica e Tecnológica.</t>
+          <t>Painéis de Dados</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2220,12 +2159,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2235,7 +2174,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/seminario-estruturas-em-aco-ensino-e-pesquisa-cientifica-e-tecnologica</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/dados-abertos/paineis-de-dados</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2243,21 +2182,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bolsas e Estudantes</t>
+          <t>Procedimentos e Processos Correcionais</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2267,12 +2204,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2282,7 +2219,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas</t>
+          <t>https://www.gov.br/cnpq/pt-br/acesso-a-informacao/corregedoria/procedimentos-e-processos-correcionais</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2290,21 +2227,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Edital seleção</t>
+          <t>Painel de Corregedorias da Corregedoria Geral da União (CRG)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2314,12 +2249,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2329,7 +2264,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servidores/edital-selecao</t>
+          <t>https://centralpaineis.cgu.gov.br/visualizar/corregedorias</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2337,21 +2272,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bolsas e Auxílios Internacionais</t>
+          <t>Painel dos Comitês Assessores</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2361,12 +2294,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2376,7 +2309,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/bolsas-e-auxilios-internacionais</t>
+          <t>https://app.powerbi.com/view?r=eyJrIjoiOTYyMGFlMWItOWRmNS00ZTZkLWI2ZGItMmM4YWNhZjQ4YWQxIiwidCI6IjkyYzBjZmE5LTdlOTEtNGVhZC1hYzI5LWNkNDRhMjM4OWIwMSJ9</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2384,21 +2317,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Programas e Bolsas no País</t>
+          <t>Guias e Tutoriais</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2408,12 +2339,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2423,7 +2354,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/programas-e-bolsas-no-pais</t>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/comites-assessoramento/guias-e-tutoriais</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2431,21 +2362,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Pesquisa Pública</t>
+          <t>Canais de Atendimento</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2455,12 +2384,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2470,7 +2399,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://sei.capes.gov.br/sei/modulos/pesquisa/md_pesq_processo_pesquisar.php?acao_externa=protocolo_pesquisar&amp;acao_origem_externa=protocolo_pesquisar&amp;id_orgao_acesso_externo=1</t>
+          <t>https://www.gov.br/cnpq/pt-br/canais_atendimento</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2478,21 +2407,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Auxílio Financeiro a Projeto Educacional ou de Pesquisa e Pós-Graduação - AUXPE</t>
+          <t>Centrais de Conteúdo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2502,12 +2429,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pós-doc</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2517,7 +2444,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/prestacao-de-contas-e-cobranca-administrativa/auxilio-financeiro-a-projeto-educacional-ou-de-pesquisa-e-pos-graduacao-auxpe</t>
+          <t>https://www.gov.br/cnpq/pt-br/centrais-de-conteudo</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2525,21 +2452,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Manual Cartão Pesquisador</t>
+          <t>Diretoria de Análise de Resultados e Soluções Digitais - DASD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2549,12 +2474,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2564,7 +2489,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/09042024_manual-cartao-pesquisador-capes-2024-v04.pdf</t>
+          <t>https://www.gov.br/cnpq/pt-br/composicao/diretoria-executiva-1/copy_of_diretoria-de-gestao-e-tecnologia-da-informacao-dgti</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2572,21 +2497,19 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Termo Uso e Politica de Privacidade App Pesquisador</t>
+          <t>Painel dos Comitês Assessores</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAPES</t>
+          <t>CNPq</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2596,12 +2519,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2611,7 +2534,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/termo-uso-e-politica-de-privacidade-app-pesquisador</t>
+          <t>https://app.powerbi.com/view?r=eyJrIjoiOTYyMGFlMWItOWRmNS00ZTZkLWI2ZGItMmM4YWNhZjQ4YWQxIiwidCI6IjkyYzBjZmE5LTdlOTEtNGVhZC1hYzI5LWNkNDRhMjM4OWIwMSJ9</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2619,36 +2542,34 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bolsas</t>
+          <t>Editais e resultados CAPES</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fulbright</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2658,7 +2579,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://fulbright.org.br/bolsas//bolsas-para-brasileiros</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2666,36 +2587,34 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fulbright dobra número de bolsas de doutorado sanduíche nos EUA e reajusta valores em até 120%</t>
+          <t>III Colóquio Saint Hilaire</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fulbright</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2705,7 +2624,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://fulbright.org.br/noticias/fulbright-dobra-numero-de-bolsas-de-doutorado-sanduiche-nos-eua/</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/iii-coloquio-saint-hilaire</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2713,36 +2632,34 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>other selected funding organisations</t>
+          <t>Produtos Digitais CAPES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DAAD</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2752,7 +2669,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/scholarship-database/information-on-other-funding-organisations/</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/aplicativos-capes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2760,36 +2677,34 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>important scholarship information</t>
+          <t>Painel de Monitoramento e Indicadores</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DAAD</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pesquisa</t>
+          <t>Business / AI / Research</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pesquisa / Geral</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2799,7 +2714,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.daad.de/en/study-and-research-in-germany/scholarships/important-information-for-scholarship-applicants/</t>
+          <t>https://www.gov.br/capes/pt-br/assuntos/painel-de-monitoramento-e-indicadores</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2807,60 +2722,6806 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="I51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Horizon Europe – Funding &amp; Tenders Portal</t>
+          <t>Orçamento - Evolução em reais</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Horizon Europe</t>
+          <t>CAPES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/institucional/orcamento-evolucao-em-reais</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Plano Anual de Atividades de Auditoria Interna (PAINT)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/auditorias/paint</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Relatório Anual de Atividades de Auditoria Interna (RAINT)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/auditorias/raint</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Normas e Manuais</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/auditorias/normas-e-manuais</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Relatórios Anuais da Autoridade de Monitoramento da LAI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/relatorios-anuais-da-autoridade-de-monitoramento-da-lai</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Editais de chamamento público</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/editais-de-chamamento-publico</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Painel LAI</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/acessoainformacao/pt-br/perguntas-frequentes/painel-lei-de-acesso-a-informacao</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Canais Específicos</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/canais-especificos</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Bolsas e Auxílios Internacionais</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/bolsas-e-auxilios-internacionais</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Estrutura Organizacional, cargos e contatos institucionais</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/transparencia-e-prestacao-de-contas/estrutura-organizacional-cargos-e-contatos-institucionais</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Privacidade e Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Encarregado pelo Tratamento de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/encarregado-pelo-tratamento-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Canais de Comunicação</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/canais-de-comunicacao</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Política de Privacidade e Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/politica-de-privacidade-e-protecao-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Compartilhamento de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/compartilhamento-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Centrais de Conteúdo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Redes Sociais da CAPES</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/redes-sociais-da-capes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Produtos digitais da CAPES</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/produtos-digitais-da-capes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Centrais de Atendimento</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/canais_atendimento</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Demais segmentos (ONGs, organizações sociais, etc)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/servicos/listar_servicos_segmento?segmento=publico_alvo_outros</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/temas/protecao-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Serviços para Imigrantes</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/temas/servicos-para-imigrantes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Política e Orçamento Educacionais</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/temas/politica-e-orcamento-educacional</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Canais do Executivo Federal</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/canais-do-executivo-federal</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Painel Estatístico de Pessoal</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/gestao/pt-br/acesso-a-informacao/servidores/servidores-publicos/painel-estatistico-de-pessoal</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Painel de Compras do Governo Federal</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>http://paineldecompras.economia.gov.br</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ImóveisNovoConsultar dados e baixar documentos de imóveis rurais na plataforma Meu Imóvel Rural</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/servicos/consultar-dados-de-imoveis-rurais-na-plataforma-meu-imovel-rural?origem=destaque_inst</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Mais notícias</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/noticias</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MAIS REGISTROS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/registros</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Programas Institucionais no País</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-no-pais</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Bolsas e Auxílios Internacionais</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Centrais de Atendimento</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/canais_atendimento</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Mais informações</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Editais e resultados CAPES</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/editais-e-resultados-capes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>III Colóquio Saint Hilaire</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/iii-coloquio-saint-hilaire</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Produtos Digitais CAPES</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/aplicativos-capes</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Painel de Monitoramento e Indicadores</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/painel-de-monitoramento-e-indicadores</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Orçamento - Evolução em reais</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/institucional/orcamento-evolucao-em-reais</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Plano Anual de Atividades de Auditoria Interna (PAINT)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/auditorias/paint</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Relatório Anual de Atividades de Auditoria Interna (RAINT)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/auditorias/raint</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Normas e Manuais</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/auditorias/normas-e-manuais</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Relatórios Anuais da Autoridade de Monitoramento da LAI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/relatorios-anuais-da-autoridade-de-monitoramento-da-lai</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Editais de chamamento público</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/editais-de-chamamento-publico</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Painel LAI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/acessoainformacao/pt-br/perguntas-frequentes/painel-lei-de-acesso-a-informacao</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Canais Específicos</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servico-de-informacao-ao-cidadao-sic/canais-especificos</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Bolsas e Auxílios Internacionais</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/bolsas-e-auxilios-internacionais</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estrutura Organizacional, cargos e contatos institucionais</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/transparencia-e-prestacao-de-contas/estrutura-organizacional-cargos-e-contatos-institucionais</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Privacidade e Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Encarregado pelo Tratamento de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/encarregado-pelo-tratamento-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Canais de Comunicação</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/canais-de-comunicacao</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Política de Privacidade e Proteção de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/politica-de-privacidade-e-protecao-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Compartilhamento de Dados Pessoais</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/privacidade-e-protecao-de-dados-pessoais/compartilhamento-de-dados-pessoais</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Centrais de Conteúdo</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Redes Sociais da CAPES</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/redes-sociais-da-capes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Produtos digitais da CAPES</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/produtos-digitais-da-capes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Centrais de Atendimento</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/canais_atendimento</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Career Fair</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Fulbright</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://fulbright.org/2019-career-fair/</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Travel Grants</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Fulbright</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://fulbright.org/2018-conference-travel-grants/</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Career Fair</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Fulbright</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://fulbright.org/2019-career-fair/</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Travel Grants</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Fulbright</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://fulbright.org/2018-conference-travel-grants/</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>frfrançais</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CORDIS EU</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
           <t>Europa</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Pesquisa</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Doutorado/Pós-doc</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Variável</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Sim</t>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://cordis.europa.eu/fr</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Research and Innovation community platform of the European Commission</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CORDIS EU</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://research-and-innovation.ec.europa.eu/index_en</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>NewsTrending SciencePut the burger and fries down – it’s not just your waistline that will thank you30 April 2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CORDIS EU</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://cordis.europa.eu/article/id/465164-put-the-burger-and-fries-down-it-s-not-just-your-waistline-that-will-thank-you</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>EU Research and Innovation data at your fingertips(opens in new window)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CORDIS EU</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/horizon-dashboard</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Semi-Automatic Project Classification - Explainability Notice</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CORDIS EU</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://cordis.europa.eu/about/explainability</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Research and innovation(opens in new window)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CORDIS EU</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://research-and-innovation.ec.europa.eu</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Apply for funding</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/apply-for-funding/</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Apply for funding</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/apply-for-funding/</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Funding finder</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Improving your funding experience</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/apply-for-funding/improving-your-funding-experience/</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Getting your funding</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/manage-your-award/getting-your-funding/</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>About UK Research and Innovation</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/who-we-are/about-uk-research-and-innovation/</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BBSRC standard research grant: applicant-led mode</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/bbsrc-standard-research-grant-applicant-led-mode/</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/contracts-for-innovation-cyber-scale-in-critical-sectors/</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: round 8</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/adopt-facilitator-support-grant-round-8/</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellowships</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>MSCA</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/actions/postdoctoral-fellowships</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I127" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J127" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>Bolsas e Estudantes</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas</t>
+        </is>
+      </c>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>Bolsas e Auxílios Internacionais</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/bolsas-e-auxilios-internacionais</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I129" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J129" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>Programas e Bolsas no País</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/perguntas-frequentes/programas-e-bolsas-no-pais</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I130" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>Serviços para Imigrantes</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/temas/servicos-para-imigrantes</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I131" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>Valores de Bolsas</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/prestacao-de-contas/valores-de-bolsas</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I132" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J132" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>Apply for funding</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E133" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/apply-for-funding/</t>
+        </is>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I133" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J133" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>Funding finder</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E134" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/</t>
+        </is>
+      </c>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I134" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J134" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>Improving your funding experience</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E135" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/apply-for-funding/improving-your-funding-experience/</t>
+        </is>
+      </c>
+      <c r="H135" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I135" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J135" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>Getting your funding</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E136" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/manage-your-award/getting-your-funding/</t>
+        </is>
+      </c>
+      <c r="H136" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I136" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J136" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>BBSRC standard research grant: applicant-led mode</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E137" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/bbsrc-standard-research-grant-applicant-led-mode/</t>
+        </is>
+      </c>
+      <c r="H137" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I137" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J137" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: round 8</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E138" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/adopt-facilitator-support-grant-round-8/</t>
+        </is>
+      </c>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I138" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J138" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>BBSRC standard research grant: applicant-led mode</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E139" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t>Fri, 01 Ma</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/bbsrc-standard-research-grant-applicant-led-mode/</t>
+        </is>
+      </c>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I139" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J139" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>ADOPT Facilitator Support Grant: round 8</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 23 Ap</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/adopt-facilitator-support-grant-round-8/</t>
+        </is>
+      </c>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I140" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J140" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>Full ADOPT grant: round seven</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E141" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 14 Ap</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/full-adopt-grant-round-seven/</t>
+        </is>
+      </c>
+      <c r="H141" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I141" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J141" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>Doctoral Networks</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>MSCA</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E142" s="1" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F142" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/actions/doctoral-networks</t>
+        </is>
+      </c>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I142" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>About UK Research and Innovation</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E143" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/who-we-are/about-uk-research-and-innovation/</t>
+        </is>
+      </c>
+      <c r="H143" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I143" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/contracts-for-innovation-cyber-scale-in-critical-sectors/</t>
+        </is>
+      </c>
+      <c r="H144" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I144" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J144" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E145" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>Wed, 29 Ap</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/contracts-for-innovation-cyber-scale-in-critical-sectors/</t>
+        </is>
+      </c>
+      <c r="H145" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I145" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J145" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>Advanced manufacturing supply chain innovation: CRD</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E146" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 21 Ap</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/advanced-manufacturing-supply-chain-innovation-crd/</t>
+        </is>
+      </c>
+      <c r="H146" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I146" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J146" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>Battery innovation concept development round 2</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E147" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F147" s="1" t="inlineStr">
+        <is>
+          <t>Mon, 20 Ap</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/battery-innovation-concept-development-round-2/</t>
+        </is>
+      </c>
+      <c r="H147" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I147" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J147" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>Contracts for Innovation: enabling commercial quantum networking</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E148" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F148" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 16 Ap</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/contracts-for-innovation-enabling-commercial-quantum-networking/</t>
+        </is>
+      </c>
+      <c r="H148" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I148" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J148" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>Doctoral focal award: environmental evidence synthesis</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E149" s="1" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F149" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 14 Ap</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/doctoral-focal-award-environmental-evidence-synthesis/</t>
+        </is>
+      </c>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I149" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Frontier artificial intelligence discovery</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E150" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 09 Ap</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/frontier-artificial-intelligence-discovery/</t>
+        </is>
+      </c>
+      <c r="H150" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I150" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J150" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>Prêmio CAPES/Fundação Grupo Volkswagen de Excelência em Pesquisa em Mobilidade Urbana Sustentável</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E151" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F151" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-fundacao-grupo-volkswagen-de-excelencia-em-pesquisa-em-mobilidade-urbana-sustentavel</t>
+        </is>
+      </c>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I151" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>Prêmio CAPES - Natura Campus de Excelência em Pesquisa</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E152" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F152" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-natura</t>
+        </is>
+      </c>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I152" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>Prêmio Top User Award/CAPES 2014</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E153" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F153" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/premios/premio-capes-proquest</t>
+        </is>
+      </c>
+      <c r="H153" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I153" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>I Encontro de Coordenadores do Programa Novos Talentos</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E154" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/i-encontro-de-coordenadores-do-programa-novos-talentos</t>
+        </is>
+      </c>
+      <c r="H154" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I154" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>I Seminário Nacional do Programa de Consolidação das Licenciaturas (Prodocência)</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E155" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F155" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/i-seminario-nacional-do-prodocencia</t>
+        </is>
+      </c>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I155" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>Seminário Estruturas em Aço, Ensino e Pesquisa Científica e Tecnológica.</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E156" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F156" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/assuntos/eventos/seminario-estruturas-em-aco-ensino-e-pesquisa-cientifica-e-tecnologica</t>
+        </is>
+      </c>
+      <c r="H156" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I156" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>Ações e Programas</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E157" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F157" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas</t>
+        </is>
+      </c>
+      <c r="H157" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I157" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>Chamadas públicas</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/licitacoes-e-contratos/chamadas-publicas</t>
+        </is>
+      </c>
+      <c r="H158" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I158" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>Edital seleção</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/servidores/edital-selecao</t>
+        </is>
+      </c>
+      <c r="H159" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>Pesquisa Pública</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>https://sei.capes.gov.br/sei/modulos/pesquisa/md_pesq_processo_pesquisar.php?acao_externa=protocolo_pesquisar&amp;acao_origem_externa=protocolo_pesquisar&amp;id_orgao_acesso_externo=1</t>
+        </is>
+      </c>
+      <c r="H160" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>Programas, Projetos e Ações</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/transparencia-e-prestacao-de-contas/programas-projetos-e-acoes</t>
+        </is>
+      </c>
+      <c r="H161" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I161" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>Auxílio Financeiro a Projeto Educacional ou de Pesquisa e Pós-Graduação - AUXPE</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E162" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F162" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/prestacao-de-contas-e-cobranca-administrativa/auxilio-financeiro-a-projeto-educacional-ou-de-pesquisa-e-pos-graduacao-auxpe</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>Manual Cartão Pesquisador</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/centrais-de-conteudo/documentos/09042024_manual-cartao-pesquisador-capes-2024-v04.pdf</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Programas, Projetos, Ações, Obras e Atividades</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/transparencia-e-prestacao-de-contas/programas-projetos-e-acoes</t>
+        </is>
+      </c>
+      <c r="H164" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>Educação e Pesquisa</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F165" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/pt-br/noticias/educacao-e-pesquisa</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>Programas Institucionais no País</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-no-pais</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Programas Estratégicos</t>
+        </is>
+      </c>
+      <c r="B167" s="1" t="inlineStr">
+        <is>
+          <t>CAPES</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/programas-estrategicos</t>
+        </is>
+      </c>
+      <c r="H167" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>European Research Executive Agency (REA)</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>MSCA</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F168" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>https://rea.ec.europa.eu/funding-and-grants/horizon-europe-marie-sklodowska-curie-actions_en</t>
+        </is>
+      </c>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Manage your award</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F169" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/manage-your-award/</t>
+        </is>
+      </c>
+      <c r="H169" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>Develop your application</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/apply-for-funding/develop-your-application/</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>Research culture</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/what-we-do/supporting-healthy-research-and-innovation-culture/</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Our strategy</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F172" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/who-we-are/our-vision-and-strategy/</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Research England</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E173" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F173" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/research-england/</t>
+        </is>
+      </c>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>Biotechnology and Biological Sciences Research Council (BBSRC)</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/bbsrc/</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I174" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>BBSRC new investigator award: applicant-led mode</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F175" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/bbsrc-new-investigator-award-applicant-led-mode/</t>
+        </is>
+      </c>
+      <c r="H175" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>Natural Environment Research Council (NERC)</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F176" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/nerc/</t>
+        </is>
+      </c>
+      <c r="H176" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Medical Research Council (MRC)</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E177" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F177" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/mrc/</t>
+        </is>
+      </c>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>UKRI metascience scientometrics for research assessment (invite only)</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E178" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F178" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/ukri-metascience-scientometrics-for-research-assessment-invite-only/</t>
+        </is>
+      </c>
+      <c r="H178" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>Economic and Social Research Council (ESRC)</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E179" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F179" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/esrc/</t>
+        </is>
+      </c>
+      <c r="H179" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I179" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Arts and Humanities Research Council (AHRC)</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E180" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/ahrc/</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I180" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>Engineering and Physical Sciences Research Council (EPSRC)</t>
+        </is>
+      </c>
+      <c r="B181" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E181" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F181" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/epsrc/</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I181" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>UKRI for researchers YouTube</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>Business / AI / Research</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@ukriforresearchers</t>
+        </is>
+      </c>
+      <c r="H182" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I182" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>BBSRC new investigator award: applicant-led mode</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E183" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F183" s="1" t="inlineStr">
+        <is>
+          <t>Fri, 01 Ma</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/bbsrc-new-investigator-award-applicant-led-mode/</t>
+        </is>
+      </c>
+      <c r="H183" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I183" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>Environmental sciences: Global Partnerships Seedcorn Fund 2026</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E184" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F184" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 30 Ap</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/environmental-sciences-global-partnerships-seedcorn-fund-2026/</t>
+        </is>
+      </c>
+      <c r="H184" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I184" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>Experimental medicine stage one</t>
+        </is>
+      </c>
+      <c r="B185" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E185" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F185" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 30 Ap</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/experimental-medicine/</t>
+        </is>
+      </c>
+      <c r="H185" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I185" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>UKRI metascience scientometrics for research assessment (invite only)</t>
+        </is>
+      </c>
+      <c r="B186" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E186" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F186" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 28 Ap</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/ukri-metascience-scientometrics-for-research-assessment-invite-only/</t>
+        </is>
+      </c>
+      <c r="H186" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I186" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Video games and gambling-related harms</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E187" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F187" s="1" t="inlineStr">
+        <is>
+          <t>Fri, 24 Ap</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/video-games-and-gambling-related-harms/</t>
+        </is>
+      </c>
+      <c r="H187" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I187" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>NHS fit for the future dementia challenge</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E188" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F188" s="1" t="inlineStr">
+        <is>
+          <t>Wed, 22 Ap</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/nhs-fit-for-the-future-dementia-challenge/</t>
+        </is>
+      </c>
+      <c r="H188" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I188" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
+        </is>
+      </c>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E189" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F189" s="1" t="inlineStr">
+        <is>
+          <t>Wed, 22 Ap</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/innovate-uk-venture-builder-pilot-expression-of-interest/</t>
+        </is>
+      </c>
+      <c r="H189" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I189" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>Growth cohorts: next generation low carbon concrete cohort entry</t>
+        </is>
+      </c>
+      <c r="B190" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F190" s="1" t="inlineStr">
+        <is>
+          <t>Mon, 20 Ap</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/growth-cohorts-next-generation-low-carbon-concrete-cohort-entry/</t>
+        </is>
+      </c>
+      <c r="H190" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I190" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>Future offshore wind technologies: feasibility studies</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F191" s="1" t="inlineStr">
+        <is>
+          <t>Fri, 17 Ap</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/future-offshore-wind-technologies-feasibility-studies/</t>
+        </is>
+      </c>
+      <c r="H191" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I191" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>2026 to 2027 strategic Longer and Larger (sLoLa) outlines</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E192" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F192" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 16 Ap</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/2026-to-2027-strategic-longer-and-larger-slola-outlines/</t>
+        </is>
+      </c>
+      <c r="H192" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I192" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>Frontier AI Benchmarking Datasets</t>
+        </is>
+      </c>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t>UKRI RSS</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E193" s="1" t="inlineStr">
+        <is>
+          <t>Geral</t>
+        </is>
+      </c>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 14 Ap</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/frontier-ai-benchmarking-datasets/</t>
+        </is>
+      </c>
+      <c r="H193" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="I193" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="1" t="inlineStr">
+        <is>
+          <t>Nao</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J193"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G161" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G162" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G163" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G164" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G165" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G166" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G167" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G168" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G169" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G170" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G171" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G172" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G173" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G174" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G175" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G176" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G177" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G178" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G179" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G180" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G181" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G182" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G183" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G184" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G185" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G186" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G187" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G188" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G189" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G190" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$J$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$J$263</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J193"/>
+  <dimension ref="A1:J263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9451,8 +9451,2940 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>Chamada de Apoio a Eventos de Promoção do Empreendedorismo e da Inovação: 1ª rodada tem inscrições abertas até 28/05</t>
+        </is>
+      </c>
+      <c r="B194" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F194" s="1" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/chamada-de-apoio-a-eventos-de-promocao-do-empreendedorismo-e-da-inovacao-esta-com-inscricoes-abertas-ate-28-05</t>
+        </is>
+      </c>
+      <c r="H194" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>CNPq apoia projetos sobre métodos alternativos à experimentação animal em pesquisas; inscrições até 03/07</t>
+        </is>
+      </c>
+      <c r="B195" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F195" s="1" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/chamada-renama-nams-cnpq-publica-edital</t>
+        </is>
+      </c>
+      <c r="H195" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>Novo PCI: chamada investirá R$ 120 milhões em pesquisas de unidades vinculadas ao MCTI; inscrições até 27/05</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/cnpq-publicou-edital-do-novo-programa-de-capacitacao-institucional</t>
+        </is>
+      </c>
+      <c r="H196" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>Pesquisa ecológica: CNPq realiza reunião de avaliação do Programa Ecológico de Longa Duração</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E197" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/pesquisa-ecologica-cnpq-realiza-reuniao-de-avaliacao-do-programa-ecologico-de-longa-duracao</t>
+        </is>
+      </c>
+      <c r="H197" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>Brics para Ciência: duas chamadas do Programa-Quadro investem R$ 15 milhões em pesquisas; inscrições até 16/06</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E198" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F198" s="1" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/brics-para-ciencia-abre-inscricoes-para-chamadas-de-projetos-cientificos</t>
+        </is>
+      </c>
+      <c r="H198" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>Novo PCI: CNPq prepara lançamento de chamada que oferece bolsas a unidades de pesquisa do MCTI</t>
+        </is>
+      </c>
+      <c r="B199" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E199" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F199" s="1" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/novo-pci-cnpq-prepara-lancamento-de-chamada-que-oferece-bolsas-a-unidades-de-pesquisa-do-mcti</t>
+        </is>
+      </c>
+      <c r="H199" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>Chamada Pepe Mujica: prazo de submissões prorrogado até 18/05; confira alterações no edital</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E200" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F200" s="1" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/chamada-pepe-mujiga-prazo-de-submissoes-prorrogado-ate-18-05-confira-alteracoes-no-edital</t>
+        </is>
+      </c>
+      <c r="H200" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>Ciências Exatas e da Terra: Sílvio Salinas recebe título de Pesquisador Emérito do CNPq por pesquisas em física estatística</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E201" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F201" s="1" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/silvio-roberto-salinas-recebe-o-titulo-de-pesquisador-emerito-do-cnpq-pela-trajetoria-de-60-anos-de-atividades-cientificas</t>
+        </is>
+      </c>
+      <c r="H201" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Conheça os novos contemplados com o título de Pesquisador(a) Emérito(a) do CNPq</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F202" s="1" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/cnpq-divulga-os-contemplados-com-o-titulo-de-pesquisador-emerito-edicao-2026</t>
+        </is>
+      </c>
+      <c r="H202" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>Ciências da Saúde: Zelinda Leão recebe título de Pesquisadora Emérita do CNPq por pesquisas sobre conservação de corais</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/uma-vida-dedicada-ao-estudo-dos-processos-naturais-atuantes-nas-areas-de-recife</t>
+        </is>
+      </c>
+      <c r="H203" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>Ciências Agrárias: Margarida Aguiar-Perecin recebe título de Pesquisadora Emérita do CNPq por estudos na área de Citogenética  e Citogenômica Vegetal</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F204" s="1" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/margarida-rodrigues-de-aguiar-perecin-recebe-o-titulo-de-pesquisador-emerito-do-cnpq</t>
+        </is>
+      </c>
+      <c r="H204" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>Ciências Humanas e Sociais: Marilene da Silva Freitas recebe título de Pesquisadora Emérita por pesquisas sociais na Amazônia</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F205" s="1" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/pesquisadora-marilene-da-silva-freitas-e-agraciada-com-o-titulo-de-pesquisador-emerito-do-cnpqs-em-ciencias-sociais-voltadas-a-regiao-amazonica</t>
+        </is>
+      </c>
+      <c r="H205" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>Engenharias: Álvaro Prata recebe título de Pesquisador Emérito do CNPq por pesquisas sobre mecânica de fluidos</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F206" s="1" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/alvaro-prata-e-contemplado-com-titulo-de-pesquisador-emerito-do-cnpq</t>
+        </is>
+      </c>
+      <c r="H206" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>Ciências da Saúde: Aldina Barral recebe título de Pesquisadora Emérita do CNPq por pesquisas na área de parasitologia</t>
+        </is>
+      </c>
+      <c r="B207" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F207" s="1" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/pesquisadora-aldina-barral-da-fiocruz-ba-e-contemplada-com-titulo-de-pesquisadora-emerita-do-cnpq</t>
+        </is>
+      </c>
+      <c r="H207" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>75 anos do CNPq: Conselho está presente em todas as fases da vida do pesquisador</t>
+        </is>
+      </c>
+      <c r="B208" s="1" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E208" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F208" s="1" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/cnpq-em-acao/75-anos-do-cnpq-conselho-esta-presente-em-todas-as-fases-da-vida-do-pesquisador</t>
+        </is>
+      </c>
+      <c r="H208" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
+        </is>
+      </c>
+      <c r="B209" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F209" s="1" t="inlineStr">
+        <is>
+          <t>Wed, 22 Ap</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/innovate-uk-venture-builder-pilot-expression-of-interest/</t>
+        </is>
+      </c>
+      <c r="H209" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>Advanced manufacturing supply chain innovation: CRD</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D210" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E210" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F210" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 21 Ap</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/advanced-manufacturing-supply-chain-innovation-crd/</t>
+        </is>
+      </c>
+      <c r="H210" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>Battery innovation concept development round 2</t>
+        </is>
+      </c>
+      <c r="B211" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F211" s="1" t="inlineStr">
+        <is>
+          <t>Mon, 20 Ap</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/battery-innovation-concept-development-round-2/</t>
+        </is>
+      </c>
+      <c r="H211" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>Contracts for Innovation: enabling commercial quantum networking</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F212" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 16 Ap</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/contracts-for-innovation-enabling-commercial-quantum-networking/</t>
+        </is>
+      </c>
+      <c r="H212" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>Full ADOPT grant: round seven</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F213" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 14 Ap</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/full-adopt-grant-round-seven/</t>
+        </is>
+      </c>
+      <c r="H213" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>Doctoral focal award: environmental evidence synthesis</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F214" s="1" t="inlineStr">
+        <is>
+          <t>Tue, 14 Ap</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/doctoral-focal-award-environmental-evidence-synthesis/</t>
+        </is>
+      </c>
+      <c r="H214" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>Frontier artificial intelligence discovery</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D215" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F215" s="1" t="inlineStr">
+        <is>
+          <t>Thu, 09 Ap</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/frontier-artificial-intelligence-discovery/</t>
+        </is>
+      </c>
+      <c r="H215" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>Financiamento</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F216" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G216" s="1" t="inlineStr"/>
+      <c r="H216" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>Programas de Financiamento</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E217" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F217" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/</t>
+        </is>
+      </c>
+      <c r="H217" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E218" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F218" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/internacional/</t>
+        </is>
+      </c>
+      <c r="H218" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>Emprego Científico</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E219" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F219" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/emprego-cientifico/</t>
+        </is>
+      </c>
+      <c r="H219" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>Projetos I&amp;D</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E220" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F220" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/projetos-id/</t>
+        </is>
+      </c>
+      <c r="H220" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>Instituições de I&amp;D</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E221" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F221" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/instituicoes-de-id/</t>
+        </is>
+      </c>
+      <c r="H221" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>Infraestruturas</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F222" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/infraestruturas-de-investigacao/</t>
+        </is>
+      </c>
+      <c r="H222" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>Outros Apoios</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E223" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F223" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/outros-apoios/</t>
+        </is>
+      </c>
+      <c r="H223" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>Concursos Abertos</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E224" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/concursos?tab=open&amp;paged=1</t>
+        </is>
+      </c>
+      <c r="H224" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>Concursos Previstos</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/concursos?tab=scheduled&amp;paged=1</t>
+        </is>
+      </c>
+      <c r="H225" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>Concursos Fechados</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F226" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/concursos?tab=closed&amp;paged=1</t>
+        </is>
+      </c>
+      <c r="H226" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>Calendário de Concursos FCT 2026</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E227" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F227" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/wp-content/uploads/2026/03/CalendarioConcursosFCT_2026.pdf</t>
+        </is>
+      </c>
+      <c r="H227" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>Instituições I&amp;D</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F228" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/concursos?tab=closed&amp;paged=1&amp;type=5</t>
+        </is>
+      </c>
+      <c r="H228" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>Serviços digitais: Tecnologia para o Conhecimento</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F229" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/servicos-de-ct/unidade-fccn-tecnologia-para-o-conhecimento/</t>
+        </is>
+      </c>
+      <c r="H229" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>Arquivo, Documentação e Informação</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F230" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/servicos-de-ct/arquivo-documentacao-e-informacao/</t>
+        </is>
+      </c>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>Acesso a dados estatísticos para fins científicos – Protocolo INE/DGEEC/FCT</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F231" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/servicos-de-ct/acesso-a-dados-estatisticos-para-fins-cientificos-protocolo-ine-dgeec-fct/</t>
+        </is>
+      </c>
+      <c r="H231" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>Balcão da Ciência</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E232" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F232" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/servicos-de-ct/balcao-da-ciencia/</t>
+        </is>
+      </c>
+      <c r="H232" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>Notas de Imprensa</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F233" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/media/notas-de-imprensa/</t>
+        </is>
+      </c>
+      <c r="H233" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>Media e Identidade de Marca</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F234" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/media/media-e-identidade-de-marca/</t>
+        </is>
+      </c>
+      <c r="H234" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>Subscrever Newsletter</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F235" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>https://signup.e2ma.net/signup/1826429/1781381/</t>
+        </is>
+      </c>
+      <c r="H235" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>Subscrever Direct Mail de Concursos FCT</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F236" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>https://forms.office.com/e/Sq7GvAdvFC</t>
+        </is>
+      </c>
+      <c r="H236" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>90 Segundos de Ciência</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F237" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/media/90-segundos-de-ciencia/</t>
+        </is>
+      </c>
+      <c r="H237" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>Subscrever Direct Mail de Concursos</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E238" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F238" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>https://forms.office.com/pages/responsepage.aspx?id=0aBHeQvToEyYmDfUhhxlnF2q_mAMig1Jk4YBMQwuPNhURUo0V1dFQkZKWUtVTjhHQ0VFNFg5RlZEUy4u&amp;route=shorturl</t>
+        </is>
+      </c>
+      <c r="H238" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>Transparência</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E239" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F239" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/politicas-de-transparencia/</t>
+        </is>
+      </c>
+      <c r="H239" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>Estudos e Planeamento Estratégico</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/estudos-e-planeamento-estrategico/</t>
+        </is>
+      </c>
+      <c r="H240" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>Documentos de Gestão</t>
+        </is>
+      </c>
+      <c r="B241" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F241" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/documentos-de-gestao/</t>
+        </is>
+      </c>
+      <c r="H241" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>Apoios Comunitários</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E242" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F242" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/apoios-comunitarios/</t>
+        </is>
+      </c>
+      <c r="H242" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>A FCT em Números</t>
+        </is>
+      </c>
+      <c r="B243" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F243" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/a-fct-em-numeros/</t>
+        </is>
+      </c>
+      <c r="H243" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>Acreditação, Certificação e Benefícios Fiscais</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F244" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/acreditacao-certificacao-e-beneficios-fiscais/</t>
+        </is>
+      </c>
+      <c r="H244" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>Recrutamento, Aquisição de Serviços e Parcerias</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F245" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/recrutamento-aquisicao-de-servicos-e-parcerias/</t>
+        </is>
+      </c>
+      <c r="H245" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>Consultas públicas</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E246" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F246" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/consultas-publicas/</t>
+        </is>
+      </c>
+      <c r="H246" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>Manifestações de Interesse</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E247" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F247" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/manifestacao-de-interesse/</t>
+        </is>
+      </c>
+      <c r="H247" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>FCCN, serviços digitais da FCT</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fccn.pt/</t>
+        </is>
+      </c>
+      <c r="H248" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>Canais de Denúncias</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E249" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F249" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/sobre/politicas-de-transparencia/canais-de-denuncias/</t>
+        </is>
+      </c>
+      <c r="H249" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>Apoios PRR – “Ciência + Digital” e “Ciência + Capacitação”</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F250" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/apoios-prr-ciencia-digital-e-ciencia-capacitacao/</t>
+        </is>
+      </c>
+      <c r="H250" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>Ciência Vitae</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F251" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cienciavitae.pt/</t>
+        </is>
+      </c>
+      <c r="H251" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>Assistente virtual</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E252" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F252" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G252" s="1" t="inlineStr"/>
+      <c r="H252" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>Bolsas de Investigação para Doutoramento</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E253" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F253" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/bolsas-de-investigacao-para-doutoramento/</t>
+        </is>
+      </c>
+      <c r="H253" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>Bolsas em todos os domínios científicosO concurso de bolsas de investigação para doutoramento em todos os domínios científicos tem periodicidade anual e integra o conjunto dos grandes concursos estruturantes da FCT</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F254" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/bolsas/bolsas-de-doutoramento-em-todos-os-dominios-cientificos/</t>
+        </is>
+      </c>
+      <c r="H254" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>Bolsas de Doutoramento  Maria de SousaO concurso para Bolsas de Investigação para Doutoramento Maria de Sousa é orientado para a obtenção de novos conhecimentos na área da virologia</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E255" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F255" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/financiamento/programas-de-financiamento/bolsas/bolsas-de-investigacao-para-doutoramento-maria-de-sousa/</t>
+        </is>
+      </c>
+      <c r="H255" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>Encerrado amar 2026Concurso Bolsas de Doutoramento 2026 – Linha de Candidatura GeralAs Bolsas de Investigação para Doutoramento destinam-se a financiar a realização de atividades de investigação conducentes à obtenção do grau académico de doutor.</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E256" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F256" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/concursos/concurso-bolsas-de-doutoramento-2026-linha-de-candidatura-geral</t>
+        </is>
+      </c>
+      <c r="H256" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>Encerrado amar 2026Concurso Bolsas de Doutoramento 2026 – Linha de Candidatura Específica em Ambiente Não AcadémicoAs Bolsas de Investigação para Doutoramento a atribuir na Linha de Candidatura Específica destinam-se a financiar a realização de atividades de investigação conducentes à obtenção do grau académico de doutor, desenvolvidas em estreita articulação com entidades não académicas.</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F257" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/concursos/concurso-bolsas-de-doutoramento-2026-linha-de-candidatura-especifica-em-ambiente-nao-academico</t>
+        </is>
+      </c>
+      <c r="H257" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>Encerrado aabr 2025Concurso Bolsas de Doutoramento 2025 – Linha de Candidatura GeralAs Bolsas de Investigação para Doutoramento destinam-se a financiar a realização, pelo/a bolseiro/a, de atividades de investigação conducentes à obtenção do grau académico de doutor.</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F258" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/concursos/concurso-bolsas-de-doutoramento-2025-linha-de-candidatura-geral</t>
+        </is>
+      </c>
+      <c r="H258" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>Calendarização FCT 2026</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F259" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/wp-content/uploads/2026/03/CalendarioConcursosFCT_2026.pdf</t>
+        </is>
+      </c>
+      <c r="H259" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>Política de Privacidade e Protecção de Dados</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F260" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/politica-de-privacidade-e-proteccao-de-dados/</t>
+        </is>
+      </c>
+      <c r="H260" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>Política de Cookies</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/politica-de-cookies/</t>
+        </is>
+      </c>
+      <c r="H261" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>Perguntas Frequentes</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F262" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt/faq/</t>
+        </is>
+      </c>
+      <c r="H262" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Acessibilidade</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="inlineStr">
+        <is>
+          <t>FCT Portugal</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F263" s="1" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fct.pt//www.fct.pt/acessibilidade</t>
+        </is>
+      </c>
+      <c r="H263" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J193"/>
+  <autoFilter ref="A1:J263"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId2"/>
@@ -9521,6 +12453,74 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G191" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G192" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G193" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G194" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G195" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G196" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G197" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G198" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G199" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G200" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G201" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G202" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G203" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G204" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G205" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G206" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G207" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G208" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G209" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G210" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G211" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G212" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G213" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G214" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G215" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G217" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G218" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G219" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G220" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G221" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G222" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G223" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G224" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G225" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G226" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G227" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G228" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G229" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G230" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G231" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G232" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G233" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G234" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G235" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G236" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G237" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G238" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G239" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G240" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G241" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G242" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G243" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G244" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G245" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G246" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G247" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G248" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G249" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G250" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G251" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G253" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G254" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G255" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G256" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G257" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G258" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G259" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G260" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G261" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G262" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G263" r:id="rId135"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="000070C0"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +47,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,11 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -483,8 +494,440 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BRAFITEC - BRASIL FRANÇA ENGENHARIA TECNOLOGIA - BRAFITEC – Edital nº 09/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/franca/programa-capes-brafitec</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CAPES/COFECUB (COMITÊ FRANCÊS DE AVALIAÇÃO DA COOPERAÇÃO UNIVERSITÁRIA COM O BRASIL) - COFECUB - Edital nº 07/2026 - Pesquisador Experiente</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/franca/cofecub</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMA CÁTEDRA - Cátedra Jorge Amado 11/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30/12/2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://inscricao.capes.gov.br/edital/CTDJORGE2026</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMA CÁTEDRA - Cátedra Rio Branco - King's College London - Edital nº 21/2024 - 3ª Chamada</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/reino-unido/catedra-rio-branco-kings-college</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMA CÁTEDRA - Cátedra Tubingen 2024 – Edital 20/2024 - 2ª Chamada</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/reino-unido/programa-catedra-tubingen</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMA BOLSAS PARA PESQUISA - CAPES/HUMBOLDT - HUMBOLDT - Edital nº 14/2022 - 26ª Chamada – Pesquisador Experiente</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Bolsa</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/alemanha/programa-bolsas-para-pesquisa-capeshumboldt</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MES CUBA DOCENTE - CAPES/MES CUBA - MESCUBA  DOCENTES 13/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Bolsa</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://inscricao.capes.gov.br/edital/MESCUBADOC2025</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>PROBRAL - PROJETOS DE COOPERAÇÃO EM PESQUISA ENTRE O BRASIL E A ALEMANHA - CAPES/DAAD - PROBRAL - Edital nº 08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/alemanha/probral</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PROGRAMAS CAPES/MATH/STIC/CLIMAT-AMSUD - PROGRAMAS CAPES/MATH/STIC/CLIMAT-AMSUD EDITAL n° 10/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/multinacional/programa-stic-amsud-capes</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>DOUTORADO PLENO EM PURDUE - CAPES/PURDUE UNIVERSITY - Purdue 05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/capes/pt-br/acesso-a-informacao/acoes-e-programas/bolsas/bolsas-e-auxilios-internacionais/encontre-aqui/paises/estados-unidos/programa-capes-purdue-para-projetos-conjuntos-de-pesquisa</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H11"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -914,8 +914,218 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Chamada CNPq/SETEC/MCTI N° 13/2026 - Apoio a Eventos de Promoção do Empreendedorismo e da Inovação no Brasil</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CNPq (Chamadas Abertas)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-13-2026/chamada-publica-cnpq-N-13-2026</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Chamada CNPq/MCTI/FNDCT Nº 12/2026 - Programa PCI</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CNPq (Chamadas Abertas)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-12-2026/chamada-publica-cnpq-N-12-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Chamada CNPq/MCTI Nº 11/2026 – RENAMA e NAMs</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>CNPq (Chamadas Abertas)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-11-2026/chamada-publica-cnpq-N-11-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Pública MCTI/CNPq Nº 02/2026 Programa de Cooperação Latino-Americana e Caribenha em Ciência, Tecnologia e Inovação - PROSUL Pepe Mujica</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>CNPq (Chamadas Abertas)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2026/chamada-no-02-2026/chamada-publica-mcti-cnpq-no-02-2026-programa-de-cooperacao-latino-americana-e-caribenha-em-ciencia-tecnologia-e-inovacao-prosul-pepe-mujica</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Nº 28/2025 - Apoio a Projetos de Cooperação CNPq-TUBITAK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CNPq (Chamadas Abertas)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/chamadas/todas-as-chamadas/chamadas-2025/chamada-no-28-2025/chamada-no-28-2025-apoio-a-projetos-de-cooperacao-cnpq-tubitak</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -927,6 +1137,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -1124,8 +1124,4124 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-EIC-PATHFINDERCHALLENGES-01-02 - Biotechnology for Healthy Ageing</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON EIC Grants / 43108390</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-PATHFINDERCHALLENGES-01-02</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-EIC-2026-PATHFINDERCHALLENGES-01-03 - DeepRAP: Deep Reasoning, Abstraction &amp; Planning towards trustworthy Cognitive AI Systems</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON EIC Grants / 43108390</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PATHFINDERCHALLENGES-01-03</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-EIC-2026-PATHFINDERCHALLENGES-01-01 - Advanced Materials for Miniaturised Energy Harvesting Systems</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON EIC Grants / 43108390</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIC-2026-PATHFINDERCHALLENGES-01-01</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EDF-EDIP-USI-2026-LS-IRA-MAB - Missiles, ammunition and bombs</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>EDF Lump Sum Grants / 44181033</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-USI-2026-LS-IRA-MAB</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-EIE-2026-03-CONNECT-01 - From lab to market: Strengthening the role of Technology Transfer Offices in bringing knowledge to the market</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Coordination and Support Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-EIE-2026-03-CONNECT-01</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D6-02 - Geopolitical competition and socioeconomic resilience in CCAM: an innovation and policy roadmap for EU leadership (CCAM Partnership)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D6-02</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D6-03 - Generative AI for smarter CCAM: enhancing perception, decision-making, and validation (CCAM Partnership)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D6-03</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D6-10 - Enhanced resilience in multimodal passenger transport through digital technologies and generative and discriminative AI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D6-10</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D6-01 - Flagship-pilot: large-scale demonstrations of CCAM (CCAM Partnership)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D6-01</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D6-09 - Road Safety and resilience of rural areas</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D6-09</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D6-07 - Supporting sustainable and smart urban mobility in Europe (CIVITAS)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Coordination and Support Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D6-07</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D6-06 - Increasing competitiveness and resilience of multimodal freight transport and logistics for competitive supply chains</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D6-06</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-10-D2-03 - Integrated Production and Product Development for Next-Generation Lithium-based Batteries for Mobility (BATT4EU and Made in Europe Partnerships)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-10-D2-03</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-MSCA-2026-DN-01-01 - MSCA Doctoral Networks 2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON TMA MSCA Doctoral Networks - Joint Doctorates / 43108390</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-MSCA-2026-DN-01-01</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-RAISE-2026-01-03 - RAISE Doctoral Networks for AI in Science (RAISE pilot)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON TMA MSCA Doctoral Networks / 43108390</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-RAISE-2026-01-03</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-JU-SNS-2026-FEM-STREAM-B-02 - Microelectronic – Front-End Module (FEM)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON JU Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-SNS-2026-FEM-STREAM-B-02</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CERV-2026-CHAR-LITI-CHARTER - Raising awareness of and building capacity for the EU Charter of Fundamental Rights</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>CERV Project Grants / 43251589</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CHARTER</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CERV-2026-CHAR-LITI-CIVIC - Promoting an enabling civic space</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CERV Project Grants / 43251589</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CHAR-LITI-CIVIC</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-HERITAGE-03 - AI integration in CCSI work practice: catalysing innovation and competitiveness</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-03</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-08 - Electoral integrity in the digital context</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-08</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-04 - Sustainable paths to media viability</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-04</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-06 - Making Europe a global magnet for talent - Attracting and retaining students, researchers and high-skilled workers from outside the EU</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-06</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-09 - Rethinking long-term care policy in the face of EU demographic shifts</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-09</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-07 - Fostering competences for the green transition</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-07</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-HERITAGE-07 - Preventing and fighting illicit trafficking of cultural goods</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Coordination and Support Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-07</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-02 - Open topic: Strengthen Europe's social model and sustainable competitiveness through productivity</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-02</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-08 - Strengthened implementation of the EU Pact on Migration and Asylum and a focus on inclusion, integration, and health</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-08</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-HERITAGE-02 - Boosting creative startups for disruptive innovation</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-02</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-HERITAGE-04 - Towards a fair and transparent market for cultural and creative content in the era of generative AI</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-04</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-10 - Fostering cooperation and integration between SSH and STEM research and innovation in the EU</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Coordination and Support Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-10</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-07 - Supporting post-conflict democracy and reconstruction</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-07</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-01 - Tackling gender-based violence against politically active women and LGBTIQ people</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-01</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-HERITAGE-06 - Safeguarding linguistic diversity in Europe</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-06</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-02-TRANSFO-01 - Co-funded European Partnership for Social Transformations and Resilience</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Programme Cofund Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-02-TRANSFO-01</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-06 - Governing global commons sustainably</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-06</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-10 - Digital and media literacy as drivers for democratic and civic resilience</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-10</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-HERITAGE-05 - Creative alliances: Fostering global partnerships in cultural policies and CCI innovation</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-05</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-05 - Contribution of basic skills to productivity, innovation, competitiveness and economic growth</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-05</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-04 - The impact of the use of digital tools outside school and for communication on educational outcomes and mental health</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-04</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-05 - Research and Innovation Network for a Union of Equality</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Coordination and Support Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-05</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-09 - Citizenship education as part of lifelong learning</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-09</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-02 - Understanding the forms of local democracy in low-income and low-middle income countries</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-02</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-HERITAGE-01 - “Artistic intelligence” : harnessing the power of the arts to address complex challenges, enhance soft skills and boost innovation and competitiveness</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-HERITAGE-01</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-DEMOCRACY-03 - Government in transition – how governments change the way they work and prepare the civil service for the future</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-DEMOCRACY-03</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL2-2026-01-TRANSFO-03 - Tackling child poverty and ensuring disadvantaged children's access to Early Childhood Education and Care</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL2-2026-01-TRANSFO-03</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-INFRA-02 - Security challenges of the green transition in urban und peri urban areas</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-02</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-BM-01 - Advanced border surveillance and situational awareness</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-01</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-FCT-01 - Improving capabilities of law enforcement to counter climate-related challenges</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-01</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-FCT-04 - Crime prevention approaches, online and off-line, tackling the nexus between addictions and crime</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-04</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-BM-03 - Reliability of age assessment methods in the context of security and border management</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Coordination and Support Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-03</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-FCT-03 - Missing persons: prevention and investigation</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-03</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-FCT-06 - Prevention and mitigation of misuse of synthetic biology for bioterrorism purposes</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-06</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-INFRA-03 - Targeted innovative capabilities for the resilience of critical entities to natural and human-induced disasters, including hybrid scenarios</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-03</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-DRS-05 - Climate security and civil preparedness – new ways to develop pre- and post-crisis climate-change related scenarios for a more resilient Europe</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-05</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-SSRI-04 - Development of ecosystem and next-generation capabilities for a secured European Critical Communication System in civil security</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-04</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-DRS-04 - Open topic on driving innovation uptake of disaster risk solutions</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-04</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-BM-02 - Accessible and available travel facilitation</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-BM-02</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-SSRI-03 - Public procurement of innovation for security</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Public Procurement of Innovative Solutions / 43108390</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-03</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-DRS-03 - Development of innovative tools, processes, equipment and technologies through responses to disasters and emergencies for search and rescue in hazardous conditions</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-03</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-DRS-02 - Multi-hazard approach and cumulative / cascading impacts</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-02</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-SSRI-02 - Demand-led innovation in security</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Pre-commercial Procurement / 43108390</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-02</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-FCT-05 - Enhancing the security of citizens against terrorism and lone-actor violence in confined spaces such as schools</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-05</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-FCT-02 - Open topic on preventing and countering the misuse of emerging technologies for criminal purposes, including issues related to lawful access to data</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-FCT-02</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-DRS-01 - Designing new ways of risk awareness and enhanced disaster preparedness</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-DRS-01</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-INFRA-01 - Tools and processes to support stress tests of critical infrastructure</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-INFRA-01</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL3-2026-01-SSRI-01 - Open topic on supporting disruptive technological innovations for civil security</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL3-2026-01-SSRI-01</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>CERV-2026-CITIZENS-TOWN-TT - Call Town Twinning 2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>CERV Lump Sum Grants / 43251589</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CERV-2026-CITIZENS-TOWN-TT</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D4-03 - Advanced data platforms to integrate whole life carbon in building information tools, assessments, and certification (Built4People Partnership)</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-03</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D4-01 - Researching the technical, social &amp; economic factors impacting the energy performance of Smart Buildings (Built4People Partnership)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-01</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D4-08 - Full-scale demonstration of heat upgrade solutions in industrial processes</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-08</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D4-02 - Low disturbance prefabrication approaches for deep renovation of multi-storey buildings (Built4People Partnership)</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-02</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D4-04 - Validating policies and business models for affordable and sustainable housing (Built4People Partnership)</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D4-04</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-BUSINESS-02 - Understanding capital market dynamics for increased investment in New European Bauhaus projects in neighbourhoods</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-02</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-REGEN-01 - Sustainable, inclusive, affordable and beautiful solutions for thermal comfort in buildings</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-01</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-REGEN-02 - Advancing sustainable maintenance and repair measures for existing buildings</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-02</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-BUSINESS-01 - Structurally addressing homelessness through coordinated social infrastructure and services in neighbourhoods</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-01</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-BUSINESS-03 - Approaches to reuse vacant, obsolete or underutilised spaces</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-BUSINESS-03</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-REGEN-03 - Innovative solutions for the sustainable and beautiful use of vertical space</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-REGEN-03</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-PARTICIPATION-03 - Understanding inhabitant’s experiences of neighbourhoods to support their health and well-being</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-03</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D2-04 - Coordinated topic with India on recycling of EV batteries</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-04</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D2-01 - Producing battery-grade materials for electrodes through sustainable processing and refining of raw materials or developing bio-based materials (BATT4EU Partnership)</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON  Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D2-01</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL5-2026-09-D3-03 - Innovative technologies and solutions to improve wind energy systems supporting the Strategic Energy Technology (SET) Plan on wind</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-CL5-2026-09-D3-03</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-PARTICIPATION-01 - Addressing homelessness through housing-led approaches aligned with the New European Bauhaus</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-01</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-NEB-2026-01-PARTICIPATION-02 - Innovative approaches for the spatial design of neighbourhoods</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-01</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-NEB-2026-01-PARTICIPATION-02</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-CL6-2022-FARM2FORK-02-04-two-stage - Smart solutions for the use of digital technologies for small- and medium-sized, farms and farm structures</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding Call</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/competitive-calls-cs/44095153</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>DIGITAL-2023-SKILLS-05-SPECIALEDU - Specialised education programmes in key capacity areas</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding Call</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/competitive-calls-cs/46214053</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>DIGITAL-2022-SKILLS-03-SPECIALISED-EDU - Specialised education programmes or modules in key capacity areas</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding Call</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/competitive-calls-cs/45114064</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>EDF-EDIP-P-2026-FNLC-CPA-AMEW - Ammunition, missiles and other explosive weapons</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>EDF Lump Sum Grants / 44181033</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2026-FNLC-CPA-AMEW</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>EDF-EDIP-P-2026-FNLC-CPA-CDS - Counter-drone systems</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>EDF Lump Sum Grants / 44181033</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2026-FNLC-CPA-CDS</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>ESF-2026-POW - Posting of workers: enhancing administrative cooperation and access to information</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>ESF Project Grants / 43254019</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/ESF-2026-POW</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>DIGITAL-ECCC-2022-CYBER-03-TEST-CERT-CAPABILTIES - Testing and Certification Capabilities</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding Call</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/competitive-calls-cs/45430171</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-INFRA-2024-EOSC-01-03 - Enabling a network of EOSC federated and trustworthy repositories and enhancing the framework of generic and discipline specific services for data and other research digital objects</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding Call</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/competitive-calls-cs/45747793</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>DIGITAL-2024-ADVANCED-DIGITAL-07-KEYCAPACITY - Specialised Education Programmes in Key Capacity Areas</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding Call</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/competitive-calls-cs/46813062</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>EDF-EDIP-P-2026-LS-IRA-EC - Energetic components</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>EDF Lump Sum Grants / 44181033</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/EDF-EDIP-P-2026-LS-IRA-EC</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>CEF-E-2026-PCI-PMI-WORKS - Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Works</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>CEF Infrastructure Projects / 43251567</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-WORKS</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>CEF-E-2026-PCI-PMI-STUDIES - Electricity, Gas, Smart Grids, Hydrogen and CO₂ networks - Studies</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>CEF Project Grants / 43251567</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/CEF-E-2026-PCI-PMI-STUDIES</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>EuropeAid/186370/DD/ACT/ME - CIVIL SOCIETY ENGAGEMENT IN PUBLIC POLICY, LOCAL DEVELOPMENT AND THE EU INTEGRATION PROCESS</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding Call</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>https://webgate.ec.europa.eu/prospect/external/publishedcalls.htm?callId=186370</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON-JU-EUROHPC-2026-COAIF-03 - Cooperation of Artificial Intelligence Factories and Factories Antennas</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>EU Funding &amp; Tenders</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>HORIZON JU Research and Innovation Actions / 43108390</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-JU-EUROHPC-2026-COAIF-03</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H114"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -1142,6 +5258,104 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -5240,8 +5240,344 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>CP 10/26: Pró PET - Chamada Pública 10/2026 - Programa de Apoio à Educação Tutorial Pesquisa-Ensino-Extensão (Pró PET)</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-04/cp_10-2026_propet.pdf</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>CP 09/26: Interconexões Catalunha - Chamada Pública 09/2026 - Programa Interconexões em CT&amp;I: Paraná-Catalunha</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-04/cp_09-2026_intercon_catalunha.pdf</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>CP 08/26: Nexus Inovação - Chamada Pública 08/2026 - Programa Nexus Inovação</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-04/cp_programa_nexus_inovacao_aberta_aprovada_-_final_24-04-26.pdf</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>CP 05/26: Eventos - ASI (jul/26 - jan/27)</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-03/cp_05-2026_eventos_associacoes_1.pdf</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>CP 04/26: Interconexões Brasillinois - Chamada Pública 04/2026 - Programa Interconexões em CT&amp;I: Paraná-Brasillinois</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-03/cp_04-2026_intercon_illinois.pdf</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>CP 15/24: Permanência de Ucranianos - Chamada Pública 15/2024 - Programa de Permanência de Cientistas Ucranianos ( Fluxo Contínuo )</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Fluxo continuo</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2024-06/cp_15-2024_permanencia_pesq_ucranianos.pdf</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>CP 10/22: Universidades Amig@s: Ucrânia - Chamada Pública 10/2022 - Programa Institucional Universidades Amig@s: Acolhimento Extensionista aos Cientistas Ucranianos ( Fluxo Contínuo )</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Fluxo continuo</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2022-04/cp_10-2022_-_extensao_ucranianos.pdf</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>CP 09/22: Acolhida a Ucranianos - Chamada Pública 09/2022 - Programa de Acolhida a Cientistas Ucranianos ( Fluxo Contínuo )</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Fluxo continuo</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2022-04/cp_09-20222_-_cientistas_ucranianas.pdf</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H122"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5356,6 +5692,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -5576,8 +5576,932 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de propostas nexBio Amazônia</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18132</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas FAPESP e University of Illinois 2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18059</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP / M-ERA.NET 2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18101</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas FAPESP/NSFC – Fundação Nacional de Ciências Naturais da China</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18122/</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas FAPESP e Universidade de Saskatchewan 2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18052</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Programa Nacional de Apoio à Geração de Empreendimentos Inovadores Programa Centelha 3 São Paulo</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18109</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas para o Programa PIPE Jornada Tecnológica - Saúde – Fase 1</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18131</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Chamada - Bolsa de Intercâmbio Internacional PRH-ANP (BEPE ANP) 2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18041</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Escolas São Paulo de Ciência Avançada (ESPCA) - 20ª Chamada</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18069</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas 2026 do PROPASP (Programa de Pesquisa Alemanha – São Paulo) – FAPESP e DAAD (Serviço Alemão de Intercâmbio Acadêmico)</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18123</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas - Iniciativa Internacional de Pesquisa sobre o Uso de Tecnologias Disruptivas para o Enfrentamento de Desafios Globais (IIDTAC)</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/17952</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas - Auxílio à Inovação Regular</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18067</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas para o Programa PIPE Jornada Tecnológica Agro – Fase 1</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18064</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Chamada FAPESP – Fundação Bracell – Fundação Itaú: Auxílio à Pesquisa para o Fortalecimento da Educação na Pré-Escola</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18030</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Chamada conjunta FAPESP-NWO 2026: Biorrefinarias Integradas para um Futuro Circular</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/17977</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas – Programa de Pesquisa em Políticas Públicas (PPPP) 2025/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/17812</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Trans-Atlantic Platform (T-AP) Preparing for Tomorrow – Societies and Strategies in Times of Transition</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18135</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP-BBSRC Pump-Priming Award (FAPPA)</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>http://www.fapesp.br/11999</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Chamada FAPESP - National Science Foundation, Diretoria de Geociências</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/17293</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Chamada FAPESP/Confap/Horizon Europe</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/16466</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>DFG</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/acordos-dfg</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>UK Research and Innovation (UKRI)</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>http://www.fapesp.br/10273</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H122"/>
+  <autoFilter ref="A1:H144"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5700,6 +6624,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -6500,8 +6500,92 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Stanford Cancer Research Education Program (SCREP)</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>NIH Reporter</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>2031-04-30</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11264575</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Integrating Behavioral Pain Management to Improve Physical Activity in Family-based Behavioral Treatment for Pediatric Obesity</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>NIH Reporter</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2031-02-28</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11302411</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H144"/>
+  <autoFilter ref="A1:H146"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -6646,6 +6730,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bolsas_pesquisa.xlsx
+++ b/bolsas_pesquisa.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bolsas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bolsas'!$A$1:$H$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -6584,8 +6584,554 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>MES-CUBA Projetos - MESCUBA-PROJETOS 12/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>https://inscricao.capes.gov.br/edital/MESCUBAPROJ2026</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>PROEB - CAMINHOS AMEFRICANOS: PROGRAMA INTERCÂMBIOS SUL-SUL. EDIÇÃO MOÇAMBIQUE - PROEB - CAMINHOS AMEFRICANOS - EDIÇÃO MOÇAMBIQUE 2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>CAPES (Bertha)</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Bolsa</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>https://inscricao.capes.gov.br/edital/PROEB-CA-2026</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Prêmio Fortec de Inovação 2026: inscrições abertas até 10/05</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/oportunidades-externas/fortec-esta-com-inscricoes-abertas-ate-10-05-para-premio-de-inovacao</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Ciências Exatas e da Terra: Zelinda Leão recebe título de Pesquisadora Emérita do CNPq por pesquisas sobre conservação de corais</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/cnpq/pt-br/assuntos/noticias/premios/uma-vida-dedicada-ao-estudo-dos-processos-naturais-atuantes-nas-areas-de-recife</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>NexBio Amazônia</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18132</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas FAPESP/CONFAP/ERC 2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18135</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Chamada de Propostas FAPESP e Fundo para o Desenvolvimento da Ciência e da Tecnologia de Macau (FDCT) 2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>FAPESP (Chamadas)</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Consultar edital</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>https://fapesp.br/18167</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>CP 11/26: SEURS - Chamada Pública 11/2026 - Apoio Institucional para Participação na 44º edição do Seminário de Extensão Universitária da Região Sul – SEURS</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-05/cp_11-2026_seurs.pdf</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>CP 10/26: Pró PET ( Pesquisa-Ensino-Extensão) - Chamada Pública 10/2026 - Programa de Apoio à Educação Tutorial Pesquisa-Ensino-Extensão (Pró PET)</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>FAPPR / Fundacao Araucaria</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Chamada Publica</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fappr.pr.gov.br/sites/fundacao-araucaria/arquivos_restritos/files/documento/2026-04/cp_10-2026_propet.pdf</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Battery Innovation Programme: battery skills initiatives</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 07 Ma</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/battery-innovation-programme-battery-skills-initiatives/</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>National Materials Innovation Programme: Feasibility studies Round 2</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 05 Ma</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/national-materials-innovation-programme-feasibility-studies-round-2/</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Particle Physics Experiment Consolidated Grants 2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>UKRI</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Multiplas</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 01 Ma</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/opportunity/particle-physics-experiment-consolidated-grants-2026/</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026 Nasopharyngeal Carcinoma Gordon Research Conference</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>NIH Reporter</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>EUA</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Geral / Multiplos</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2027-04-30</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>https://reporter.nih.gov/project-details/11319955</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H146"/>
+  <autoFilter ref="A1:H159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -6732,6 +7278,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
